--- a/resource/template/shortUrl/template.xlsx
+++ b/resource/template/shortUrl/template.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26400" windowHeight="10340"/>
+    <workbookView windowHeight="16960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -28,16 +41,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
-      <sz val="11"/>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -508,147 +529,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="6" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="6" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -924,6 +954,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1180,26 +1217,26 @@
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="31.5673076923077" customWidth="1"/>
-    <col min="2" max="2" width="35.8846153846154" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6730769230769" style="1" customWidth="1"/>
+    <col min="2" max="2" width="51.1153846153846" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.4807692307692" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" ht="17.6" spans="1:3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="2"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" s="3"/>
+      <c r="B3" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
